--- a/public/downloads/GauthierSolvation2017.xlsx
+++ b/public/downloads/GauthierSolvation2017.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="56">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,16 +169,37 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
-    <t>OOH</t>
+    <t>Gas shift correction</t>
   </si>
   <si>
-    <t>OH</t>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>O</t>
   </si>
   <si>
     <t>O2</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>OOH</t>
   </si>
 </sst>
 </file>
@@ -662,10 +685,10 @@
         <v>4</v>
       </c>
       <c r="N3" s="5">
-        <v>35.91417074203491</v>
+        <v>35914.17074203491</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03282830963622935</v>
+        <v>32.82830963622936</v>
       </c>
       <c r="P3" s="5">
         <v>1094</v>
@@ -696,9 +719,7 @@
       <c r="H4" s="4">
         <v>1.653222876105003</v>
       </c>
-      <c r="I4" s="4">
-        <v>0</v>
-      </c>
+      <c r="I4" s="4"/>
       <c r="J4" s="4">
         <v>1.948308723482781</v>
       </c>
@@ -712,10 +733,10 @@
         <v>4</v>
       </c>
       <c r="N4" s="5">
-        <v>119.0352883338928</v>
+        <v>119035.2883338928</v>
       </c>
       <c r="O4" s="4">
-        <v>0.06321576650764356</v>
+        <v>63.21576650764356</v>
       </c>
       <c r="P4" s="5">
         <v>1883</v>
@@ -762,10 +783,10 @@
         <v>4</v>
       </c>
       <c r="N5" s="5">
-        <v>239.9887969493866</v>
+        <v>239988.7969493866</v>
       </c>
       <c r="O5" s="4">
-        <v>0.3041683104554963</v>
+        <v>304.1683104554963</v>
       </c>
       <c r="P5" s="5">
         <v>789</v>
@@ -812,10 +833,10 @@
         <v>4</v>
       </c>
       <c r="N6" s="5">
-        <v>57.96846151351929</v>
+        <v>57968.46151351929</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08364857361258195</v>
+        <v>83.64857361258194</v>
       </c>
       <c r="P6" s="5">
         <v>693</v>
@@ -862,10 +883,10 @@
         <v>4</v>
       </c>
       <c r="N7" s="5">
-        <v>231.3443155288696</v>
+        <v>231344.3155288696</v>
       </c>
       <c r="O7" s="4">
-        <v>0.2835101905991049</v>
+        <v>283.5101905991049</v>
       </c>
       <c r="P7" s="5">
         <v>816</v>
@@ -912,10 +933,10 @@
         <v>4</v>
       </c>
       <c r="N8" s="5">
-        <v>28.37125492095947</v>
+        <v>28371.25492095947</v>
       </c>
       <c r="O8" s="4">
-        <v>0.03623404204464811</v>
+        <v>36.23404204464811</v>
       </c>
       <c r="P8" s="5">
         <v>783</v>
@@ -946,9 +967,7 @@
       <c r="H9" s="4">
         <v>0.7508204751345444</v>
       </c>
-      <c r="I9" s="4">
-        <v>0</v>
-      </c>
+      <c r="I9" s="4"/>
       <c r="J9" s="4">
         <v>0.7875660233828354</v>
       </c>
@@ -962,10 +981,10 @@
         <v>4</v>
       </c>
       <c r="N9" s="5">
-        <v>63.91201424598694</v>
+        <v>63912.01424598694</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02975419657634401</v>
+        <v>29.75419657634401</v>
       </c>
       <c r="P9" s="5">
         <v>2148</v>
@@ -1012,10 +1031,10 @@
         <v>4</v>
       </c>
       <c r="N10" s="5">
-        <v>61.43595218658447</v>
+        <v>61435.95218658447</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08427428283482095</v>
+        <v>84.27428283482095</v>
       </c>
       <c r="P10" s="5">
         <v>729</v>
@@ -1046,9 +1065,7 @@
       <c r="H11" s="4">
         <v>0.1118266406839854</v>
       </c>
-      <c r="I11" s="4">
-        <v>0</v>
-      </c>
+      <c r="I11" s="4"/>
       <c r="J11" s="4">
         <v>0.2639019065233993</v>
       </c>
@@ -1062,10 +1079,10 @@
         <v>4</v>
       </c>
       <c r="N11" s="5">
-        <v>61.46733999252319</v>
+        <v>61467.33999252319</v>
       </c>
       <c r="O11" s="4">
-        <v>0.04178609108941073</v>
+        <v>41.78609108941073</v>
       </c>
       <c r="P11" s="5">
         <v>1471</v>
@@ -1112,10 +1129,10 @@
         <v>4</v>
       </c>
       <c r="N12" s="5">
-        <v>28.23727536201477</v>
+        <v>28237.27536201477</v>
       </c>
       <c r="O12" s="4">
-        <v>0.02264416628870471</v>
+        <v>22.64416628870471</v>
       </c>
       <c r="P12" s="5">
         <v>1247</v>
@@ -1162,10 +1179,10 @@
         <v>4</v>
       </c>
       <c r="N13" s="5">
-        <v>39.12958979606628</v>
+        <v>39129.58979606628</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07327638538589192</v>
+        <v>73.27638538589191</v>
       </c>
       <c r="P13" s="5">
         <v>534</v>
@@ -1212,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="N14" s="5">
-        <v>198.0000476837158</v>
+        <v>198000.0476837158</v>
       </c>
       <c r="O14" s="4">
-        <v>0.404081729966767</v>
+        <v>404.081729966767</v>
       </c>
       <c r="P14" s="5">
         <v>490</v>
@@ -1262,10 +1279,10 @@
         <v>4</v>
       </c>
       <c r="N15" s="5">
-        <v>344.5812447071075</v>
+        <v>344581.2447071075</v>
       </c>
       <c r="O15" s="4">
-        <v>0.4186892402273482</v>
+        <v>418.6892402273481</v>
       </c>
       <c r="P15" s="5">
         <v>823</v>
@@ -1312,10 +1329,10 @@
         <v>4</v>
       </c>
       <c r="N16" s="5">
-        <v>54.24637079238892</v>
+        <v>54246.37079238892</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09880941856537143</v>
+        <v>98.80941856537143</v>
       </c>
       <c r="P16" s="5">
         <v>549</v>
@@ -1362,10 +1379,10 @@
         <v>4</v>
       </c>
       <c r="N17" s="5">
-        <v>59.25435447692871</v>
+        <v>59254.35447692871</v>
       </c>
       <c r="O17" s="4">
-        <v>0.1155055642825121</v>
+        <v>115.5055642825121</v>
       </c>
       <c r="P17" s="5">
         <v>513</v>
@@ -1393,7 +1410,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1404,9 +1421,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1440,8 +1463,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1463,25 +1494,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2503723380505951</v>
+        <v>0.08353683517404153</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2503723380505951</v>
+        <v>0.08353683517404153</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09002526745241379</v>
+        <v>0.1391111547974644</v>
       </c>
       <c r="E3" s="4">
-        <v>78.36734693877551</v>
+        <v>83.57142857142857</v>
       </c>
       <c r="F3" s="4">
-        <v>82.14765100671141</v>
+        <v>80.97315436241611</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1504,25 +1553,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08353683517404153</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08353683517404153</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1495159198800697</v>
+        <v>0.1104880175546805</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1495159198800697</v>
+        <v>0.1104880175546805</v>
       </c>
       <c r="D4" s="4">
-        <v>0.0558659068015312</v>
+        <v>0.2111916839165202</v>
       </c>
       <c r="E4" s="4">
-        <v>85</v>
+        <v>86.83673469387755</v>
       </c>
       <c r="F4" s="4">
-        <v>88.28859060402685</v>
+        <v>80.23489932885906</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1545,25 +1610,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1104880175546805</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1104880175546805</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.161338454529119</v>
+        <v>0.04632243497934257</v>
       </c>
       <c r="C5" s="4">
-        <v>0.161338454529119</v>
+        <v>0.04632243497934257</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1670314959438031</v>
+        <v>0.1551878704670509</v>
       </c>
       <c r="E5" s="4">
-        <v>87.24489795918367</v>
+        <v>86.32653061224489</v>
       </c>
       <c r="F5" s="4">
-        <v>87.38255033557047</v>
+        <v>83.28859060402685</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1586,25 +1667,41 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.04632243497934257</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04632243497934257</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1375193714906304</v>
+        <v>0.3718682294708247</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1375193714906304</v>
+        <v>0.3718682294708247</v>
       </c>
       <c r="D6" s="4">
-        <v>0.01399425063066406</v>
+        <v>0.5060175209255542</v>
       </c>
       <c r="E6" s="4">
-        <v>82.95918367346938</v>
+        <v>81.83673469387755</v>
       </c>
       <c r="F6" s="4">
-        <v>81.61073825503355</v>
+        <v>78.7248322147651</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1627,9 +1724,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3718682294708247</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.3718682294708247</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1640,6 +1753,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1647,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1658,9 +1772,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1694,8 +1814,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1717,25 +1845,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.03691064180252912</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>1.006053801223662</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.3399234897029197</v>
+        <v>0.961687918350127</v>
       </c>
       <c r="E3" s="4">
-        <v>55.10204081632653</v>
+        <v>31.59863945578232</v>
       </c>
       <c r="F3" s="4">
-        <v>43.78076062639821</v>
+        <v>26.73378076062641</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -1758,25 +1902,37 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>1.006053801223662</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.06360711138003322</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
+        <v>0.8688926199966991</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.2111767677521035</v>
+        <v>0.8992099265152538</v>
       </c>
       <c r="E4" s="4">
-        <v>58.06122448979592</v>
+        <v>33.19727891156463</v>
       </c>
       <c r="F4" s="4">
-        <v>44.76510067114094</v>
+        <v>17.49440715883669</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -1799,25 +1955,37 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.8688926199966991</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.3462308603972462</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
+        <v>0.5742188839172646</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.4094194132536915</v>
+        <v>0.5427314190124795</v>
       </c>
       <c r="E5" s="4">
-        <v>54.28571428571428</v>
+        <v>39.65986394557824</v>
       </c>
       <c r="F5" s="4">
-        <v>45.85011185682327</v>
+        <v>28.7472035794184</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1840,25 +2008,37 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.5742188839172646</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.0005579491561329419</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
+        <v>0.5541165954005516</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.09508795538488268</v>
+        <v>0.7466348296534813</v>
       </c>
       <c r="E6" s="4">
-        <v>66.5986394557823</v>
+        <v>22.95918367346939</v>
       </c>
       <c r="F6" s="4">
-        <v>53.8814317673378</v>
+        <v>8.970917225950783</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -1881,9 +2061,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5541165954005516</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1894,6 +2088,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1901,7 +2096,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1912,9 +2107,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1948,8 +2149,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1971,148 +2180,214 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.638319146024009</v>
+        <v>0.161338454529119</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.161338454529119</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3796984070408547</v>
+        <v>0.1670314959438031</v>
       </c>
       <c r="E3" s="4">
-        <v>69.96598639455782</v>
+        <v>87.24489795918367</v>
       </c>
       <c r="F3" s="4">
-        <v>62.87472035794184</v>
+        <v>87.38255033557047</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.161338454529119</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.161338454529119</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2851470561767295</v>
+        <v>0.1375193714906304</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.1375193714906304</v>
       </c>
       <c r="D4" s="4">
-        <v>0.09984193761593846</v>
+        <v>0.01399425063066406</v>
       </c>
       <c r="E4" s="4">
-        <v>52.41496598639439</v>
+        <v>82.95918367346938</v>
       </c>
       <c r="F4" s="4">
-        <v>44.01565995525763</v>
+        <v>81.61073825503355</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1375193714906304</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1375193714906304</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2124432284087208</v>
+        <v>0.1495159198800697</v>
       </c>
       <c r="C5" s="4">
-        <v>0</v>
+        <v>0.1495159198800697</v>
       </c>
       <c r="D5" s="4">
-        <v>0.243156309768584</v>
+        <v>0.0558659068015312</v>
       </c>
       <c r="E5" s="4">
-        <v>64.72789115646223</v>
+        <v>85</v>
       </c>
       <c r="F5" s="4">
-        <v>64.39597315436211</v>
+        <v>88.28859060402685</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1495159198800697</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1495159198800697</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.1502438088363087</v>
+        <v>0.2503723380505951</v>
       </c>
       <c r="C6" s="4">
-        <v>0.1502438088363087</v>
+        <v>0.2503723380505951</v>
       </c>
       <c r="D6" s="4">
-        <v>0.02030568322595716</v>
+        <v>0.09002526745241379</v>
       </c>
       <c r="E6" s="4">
-        <v>79.31972789115646</v>
+        <v>78.36734693877551</v>
       </c>
       <c r="F6" s="4">
-        <v>68.85906040268455</v>
+        <v>82.14765100671141</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
@@ -2135,9 +2410,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2503723380505951</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2503723380505951</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2148,6 +2439,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2155,7 +2447,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2166,9 +2458,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2202,8 +2500,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2225,25 +2531,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3726643437016213</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.3462308603972462</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.1897345894444191</v>
+        <v>0.4094194132536915</v>
       </c>
       <c r="E3" s="4">
-        <v>78.67346938775511</v>
+        <v>54.28571428571428</v>
       </c>
       <c r="F3" s="4">
-        <v>71.07382550335571</v>
+        <v>45.85011185682327</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2266,132 +2588,182 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3462308603972462</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2778421493316367</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.2778421493316367</v>
-      </c>
+        <v>0.0005579491561329419</v>
+      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
-        <v>0.1949952693725303</v>
+        <v>0.09508795538488268</v>
       </c>
       <c r="E4" s="4">
-        <v>90.10204081632654</v>
+        <v>66.5986394557823</v>
       </c>
       <c r="F4" s="4">
-        <v>90.20134228187919</v>
+        <v>53.8814317673378</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0005579491561329419</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.06670987193289069</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.06670987193289069</v>
-      </c>
+        <v>0.06360711138003322</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.1011799532622364</v>
+        <v>0.2111767677521035</v>
       </c>
       <c r="E5" s="4">
-        <v>92.95918367346938</v>
+        <v>58.06122448979592</v>
       </c>
       <c r="F5" s="4">
-        <v>93.52348993288591</v>
+        <v>44.76510067114094</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06360711138003322</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.2761831780379689</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.2761831780379689</v>
-      </c>
+        <v>0.03691064180252912</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.1867962380355275</v>
+        <v>0.3399234897029197</v>
       </c>
       <c r="E6" s="4">
-        <v>89.59183673469387</v>
+        <v>55.10204081632653</v>
       </c>
       <c r="F6" s="4">
-        <v>90.06711409395973</v>
+        <v>43.78076062639821</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.03691064180252912</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2402,6 +2774,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2409,7 +2782,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2420,9 +2793,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2456,8 +2835,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2479,25 +2866,41 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2074434644116598</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
+        <v>0.2124432284087208</v>
+      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4">
-        <v>0.3551923668517309</v>
+        <v>0.243156309768584</v>
       </c>
       <c r="E3" s="4">
-        <v>79.42176870748298</v>
+        <v>64.72789115646223</v>
       </c>
       <c r="F3" s="4">
-        <v>71.17449664429529</v>
+        <v>64.39597315436211</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -2520,25 +2923,39 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2124432284087208</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2613713739371042</v>
+        <v>0.1502438088363087</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2613713739371042</v>
+        <v>0.1502438088363087</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2779157159782336</v>
+        <v>0.02030568322595716</v>
       </c>
       <c r="E4" s="4">
-        <v>99.28571428571429</v>
+        <v>79.31972789115646</v>
       </c>
       <c r="F4" s="4">
-        <v>98.02013422818791</v>
+        <v>68.85906040268455</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -2561,91 +2978,131 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1502438088363087</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1502438088363087</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.4884348768443409</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.4884348768443409</v>
-      </c>
+        <v>0.2851470561767295</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.5004397291392628</v>
+        <v>0.09984193761593846</v>
       </c>
       <c r="E5" s="4">
-        <v>98.16326530612245</v>
+        <v>52.41496598639439</v>
       </c>
       <c r="F5" s="4">
-        <v>97.22595078299777</v>
+        <v>44.01565995525763</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2851470561767295</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3081344465310254</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.3081344465310254</v>
-      </c>
+        <v>0.638319146024009</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.3392242292458691</v>
+        <v>0.3796984070408547</v>
       </c>
       <c r="E6" s="4">
-        <v>98.67346938775511</v>
+        <v>69.96598639455782</v>
       </c>
       <c r="F6" s="4">
-        <v>97.71812080536913</v>
+        <v>62.87472035794184</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.638319146024009</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2656,6 +3113,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2663,7 +3121,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2674,9 +3132,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2710,8 +3174,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2733,107 +3205,157 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>1.378204893456703</v>
+        <v>0.06670987193289069</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.06670987193289069</v>
       </c>
       <c r="D3" s="4">
-        <v>1.00330187021398</v>
+        <v>0.1011799532622364</v>
       </c>
       <c r="E3" s="4">
-        <v>63.43537414965984</v>
+        <v>92.95918367346938</v>
       </c>
       <c r="F3" s="4">
-        <v>60.68232662192379</v>
+        <v>93.52348993288591</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06670987193289069</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06670987193289069</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.6934765132213345</v>
+        <v>0.2761831780379689</v>
       </c>
       <c r="C4" s="4">
-        <v>0</v>
+        <v>0.2761831780379689</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4607870431683311</v>
+        <v>0.1867962380355275</v>
       </c>
       <c r="E4" s="4">
-        <v>70.30612244897959</v>
+        <v>89.59183673469387</v>
       </c>
       <c r="F4" s="4">
-        <v>65.14541387024607</v>
+        <v>90.06711409395973</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
       </c>
       <c r="H4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.2761831780379689</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.2761831780379689</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1338623803406511</v>
+        <v>0.2778421493316367</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1338623803406511</v>
+        <v>0.2778421493316367</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1065171998294039</v>
+        <v>0.1949952693725303</v>
       </c>
       <c r="E5" s="4">
-        <v>92.14285714285714</v>
+        <v>90.10204081632654</v>
       </c>
       <c r="F5" s="4">
-        <v>94.79865771812081</v>
+        <v>90.20134228187919</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2856,50 +3378,78 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2778421493316367</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2778421493316367</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.6256232758469986</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.6256232758469986</v>
-      </c>
+        <v>0.3726643437016213</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.5231748124070572</v>
+        <v>0.1897345894444191</v>
       </c>
       <c r="E6" s="4">
-        <v>88.16326530612245</v>
+        <v>78.67346938775511</v>
       </c>
       <c r="F6" s="4">
-        <v>92.24832214765101</v>
+        <v>71.07382550335571</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.3726643437016213</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2910,6 +3460,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2917,7 +3468,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2928,9 +3479,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2964,8 +3521,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2987,25 +3552,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.5883888638151182</v>
+        <v>0.4884348768443409</v>
       </c>
       <c r="C3" s="4">
-        <v>0.5883888638151182</v>
+        <v>0.4884348768443409</v>
       </c>
       <c r="D3" s="4">
-        <v>0.7965030110015112</v>
+        <v>0.5004397291392628</v>
       </c>
       <c r="E3" s="4">
-        <v>93.36734693877551</v>
+        <v>98.16326530612245</v>
       </c>
       <c r="F3" s="4">
-        <v>89.74272930648769</v>
+        <v>97.22595078299777</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
@@ -3028,25 +3611,41 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.4884348768443409</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.4884348768443409</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3852360097622046</v>
+        <v>0.3081344465310254</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3852360097622046</v>
+        <v>0.3081344465310254</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5484209058736929</v>
+        <v>0.3392242292458691</v>
       </c>
       <c r="E4" s="4">
-        <v>95.30612244897959</v>
+        <v>98.67346938775511</v>
       </c>
       <c r="F4" s="4">
-        <v>93.8255033557047</v>
+        <v>97.71812080536913</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -3069,25 +3668,41 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3081344465310254</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3081344465310254</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.666921432659084</v>
+        <v>0.2613713739371042</v>
       </c>
       <c r="C5" s="4">
-        <v>0.666921432659084</v>
+        <v>0.2613713739371042</v>
       </c>
       <c r="D5" s="4">
-        <v>0.6914325613231576</v>
+        <v>0.2779157159782336</v>
       </c>
       <c r="E5" s="4">
-        <v>90.40816326530613</v>
+        <v>99.28571428571429</v>
       </c>
       <c r="F5" s="4">
-        <v>89.69798657718121</v>
+        <v>98.02013422818791</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -3110,50 +3725,78 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2613713739371042</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.2613713739371042</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.3852213124329724</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.3852213124329724</v>
-      </c>
+        <v>0.2074434644116598</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.6587938169534455</v>
+        <v>0.3551923668517309</v>
       </c>
       <c r="E6" s="4">
-        <v>90.51020408163265</v>
+        <v>79.42176870748298</v>
       </c>
       <c r="F6" s="4">
-        <v>82.34899328859061</v>
+        <v>71.17449664429529</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2074434644116598</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3164,6 +3807,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3171,7 +3815,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3182,9 +3826,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3218,8 +3868,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3241,66 +3899,100 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.9862270170316867</v>
+        <v>0.1338623803406511</v>
       </c>
       <c r="C3" s="4">
-        <v>0</v>
+        <v>0.1338623803406511</v>
       </c>
       <c r="D3" s="4">
-        <v>0.6662431174385608</v>
+        <v>0.1065171998294039</v>
       </c>
       <c r="E3" s="4">
-        <v>79.18367346938776</v>
+        <v>92.14285714285714</v>
       </c>
       <c r="F3" s="4">
-        <v>75.46979865771812</v>
+        <v>94.79865771812081</v>
       </c>
       <c r="G3" s="5">
         <v>1</v>
       </c>
       <c r="H3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1338623803406511</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1338623803406511</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3948179336333412</v>
+        <v>0.6256232758469986</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3948179336333412</v>
+        <v>0.6256232758469986</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3079486044190178</v>
+        <v>0.5231748124070572</v>
       </c>
       <c r="E4" s="4">
-        <v>89.48979591836735</v>
+        <v>88.16326530612245</v>
       </c>
       <c r="F4" s="4">
-        <v>91.30872483221476</v>
+        <v>92.24832214765101</v>
       </c>
       <c r="G4" s="5">
         <v>1</v>
@@ -3323,91 +4015,131 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.6256232758469986</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.6256232758469986</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.07566750462326066</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.07566750462326066</v>
-      </c>
+        <v>0.6934765132213345</v>
+      </c>
+      <c r="C5" s="4"/>
       <c r="D5" s="4">
-        <v>0.03521192486557023</v>
+        <v>0.4607870431683311</v>
       </c>
       <c r="E5" s="4">
-        <v>93.36734693877551</v>
+        <v>70.30612244897959</v>
       </c>
       <c r="F5" s="4">
-        <v>95</v>
+        <v>65.14541387024607</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
       </c>
       <c r="H5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.6934765132213345</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B6" s="4">
-        <v>0.4358368416731873</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.4358368416731873</v>
-      </c>
+        <v>1.378204893456703</v>
+      </c>
+      <c r="C6" s="4"/>
       <c r="D6" s="4">
-        <v>0.3372979660933533</v>
+        <v>1.00330187021398</v>
       </c>
       <c r="E6" s="4">
-        <v>89.59183673469387</v>
+        <v>63.43537414965984</v>
       </c>
       <c r="F6" s="4">
-        <v>92.85234899328859</v>
+        <v>60.68232662192379</v>
       </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1.378204893456703</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3418,12 +4150,1562 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.666921432659084</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.666921432659084</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.6914325613231576</v>
+      </c>
+      <c r="E3" s="4">
+        <v>90.40816326530613</v>
+      </c>
+      <c r="F3" s="4">
+        <v>89.69798657718121</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.666921432659084</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.666921432659084</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.3852213124329724</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.3852213124329724</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.6587938169534455</v>
+      </c>
+      <c r="E4" s="4">
+        <v>90.51020408163265</v>
+      </c>
+      <c r="F4" s="4">
+        <v>82.34899328859061</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3852213124329724</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.3852213124329724</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3852360097622046</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3852360097622046</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5484209058736929</v>
+      </c>
+      <c r="E5" s="4">
+        <v>95.30612244897959</v>
+      </c>
+      <c r="F5" s="4">
+        <v>93.8255033557047</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3852360097622046</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3852360097622046</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.5883888638151182</v>
+      </c>
+      <c r="C6" s="4">
+        <v>0.5883888638151182</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0.7965030110015112</v>
+      </c>
+      <c r="E6" s="4">
+        <v>93.36734693877551</v>
+      </c>
+      <c r="F6" s="4">
+        <v>89.74272930648769</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5883888638151182</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.5883888638151182</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.07566750462326066</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.07566750462326066</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.03521192486557023</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.36734693877551</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07566750462326066</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07566750462326066</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.4358368416731873</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4358368416731873</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.3372979660933533</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.59183673469387</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.85234899328859</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4358368416731873</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.4358368416731873</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.3948179336333412</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.3948179336333412</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.3079486044190178</v>
+      </c>
+      <c r="E5" s="4">
+        <v>89.48979591836735</v>
+      </c>
+      <c r="F5" s="4">
+        <v>91.30872483221476</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3948179336333412</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.3948179336333412</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.9862270170316867</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <v>0.6662431174385608</v>
+      </c>
+      <c r="E6" s="4">
+        <v>79.18367346938776</v>
+      </c>
+      <c r="F6" s="4">
+        <v>75.46979865771812</v>
+      </c>
+      <c r="G6" s="5">
+        <v>1</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.9862270170316867</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>75</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>75</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1762576854268081</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1737327078873241</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.4341667466494369</v>
+      </c>
+      <c r="K3" s="4">
+        <v>69.45578231292519</v>
+      </c>
+      <c r="L3" s="4">
+        <v>66.34787472035796</v>
+      </c>
+      <c r="M3" s="5">
+        <v>4</v>
+      </c>
+      <c r="N3" s="5">
+        <v>35914.17074203491</v>
+      </c>
+      <c r="O3" s="4">
+        <v>32.82830963622936</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>100</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>1.653222876105003</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4">
+        <v>1.948308723482781</v>
+      </c>
+      <c r="K4" s="4">
+        <v>31.29251700680272</v>
+      </c>
+      <c r="L4" s="4">
+        <v>21.62192393736018</v>
+      </c>
+      <c r="M4" s="5">
+        <v>4</v>
+      </c>
+      <c r="N4" s="5">
+        <v>119035.2883338928</v>
+      </c>
+      <c r="O4" s="4">
+        <v>63.21576650764356</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>100</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.1126985315793985</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.1126985315793985</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.07777516810240685</v>
+      </c>
+      <c r="K5" s="4">
+        <v>82.29591836734694</v>
+      </c>
+      <c r="L5" s="4">
+        <v>82.29865771812081</v>
+      </c>
+      <c r="M5" s="5">
+        <v>4</v>
+      </c>
+      <c r="N5" s="5">
+        <v>239988.7969493866</v>
+      </c>
+      <c r="O5" s="4">
+        <v>304.1683104554963</v>
+      </c>
+      <c r="P5" s="5">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>50</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>50</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2036123699811173</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.01727518149492191</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.08720870376024319</v>
+      </c>
+      <c r="K6" s="4">
+        <v>85.13605442176872</v>
+      </c>
+      <c r="L6" s="4">
+        <v>82.30425055928413</v>
+      </c>
+      <c r="M6" s="5">
+        <v>4</v>
+      </c>
+      <c r="N6" s="5">
+        <v>57968.46151351929</v>
+      </c>
+      <c r="O6" s="4">
+        <v>83.64857361258194</v>
+      </c>
+      <c r="P6" s="5">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>50</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.2392775819790567</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.0651108850318165</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.1215476797116007</v>
+      </c>
+      <c r="K7" s="4">
+        <v>81.91326530612245</v>
+      </c>
+      <c r="L7" s="4">
+        <v>79.25615212527964</v>
+      </c>
+      <c r="M7" s="5">
+        <v>4</v>
+      </c>
+      <c r="N7" s="5">
+        <v>231344.3155288696</v>
+      </c>
+      <c r="O7" s="4">
+        <v>283.5101905991049</v>
+      </c>
+      <c r="P7" s="5">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.1530538792947223</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1530538792947223</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2528770575266474</v>
+      </c>
+      <c r="K8" s="4">
+        <v>84.64285714285714</v>
+      </c>
+      <c r="L8" s="4">
+        <v>80.80536912751678</v>
+      </c>
+      <c r="M8" s="5">
+        <v>4</v>
+      </c>
+      <c r="N8" s="5">
+        <v>28371.25492095947</v>
+      </c>
+      <c r="O8" s="4">
+        <v>36.23404204464811</v>
+      </c>
+      <c r="P8" s="5">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.7508204751345444</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4">
+        <v>0.7875660233828354</v>
+      </c>
+      <c r="K9" s="4">
+        <v>31.85374149659864</v>
+      </c>
+      <c r="L9" s="4">
+        <v>20.48657718120803</v>
+      </c>
+      <c r="M9" s="5">
+        <v>4</v>
+      </c>
+      <c r="N9" s="5">
+        <v>63912.01424598694</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.75419657634401</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>100</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.1746865209876036</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.1746865209876036</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.08172923020710303</v>
+      </c>
+      <c r="K10" s="4">
+        <v>83.39285714285714</v>
+      </c>
+      <c r="L10" s="4">
+        <v>84.85738255033557</v>
+      </c>
+      <c r="M10" s="5">
+        <v>4</v>
+      </c>
+      <c r="N10" s="5">
+        <v>61435.95218658447</v>
+      </c>
+      <c r="O10" s="4">
+        <v>84.27428283482095</v>
+      </c>
+      <c r="P10" s="5">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>100</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>100</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1118266406839854</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4">
+        <v>0.2639019065233993</v>
+      </c>
+      <c r="K11" s="4">
+        <v>58.51190476190476</v>
+      </c>
+      <c r="L11" s="4">
+        <v>47.06935123042506</v>
+      </c>
+      <c r="M11" s="5">
+        <v>4</v>
+      </c>
+      <c r="N11" s="5">
+        <v>61467.33999252319</v>
+      </c>
+      <c r="O11" s="4">
+        <v>41.78609108941073</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1471</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>25</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>75</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>75</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.321538309861442</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1502438088363087</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1857505844128336</v>
+      </c>
+      <c r="K12" s="4">
+        <v>66.60714285714322</v>
+      </c>
+      <c r="L12" s="4">
+        <v>60.03635346756165</v>
+      </c>
+      <c r="M12" s="5">
+        <v>4</v>
+      </c>
+      <c r="N12" s="5">
+        <v>28237.27536201477</v>
+      </c>
+      <c r="O12" s="4">
+        <v>22.64416628870471</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>75</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>25</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>25</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.2483498857510294</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.2069117331008321</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1681765125286783</v>
+      </c>
+      <c r="K13" s="4">
+        <v>87.83163265306122</v>
+      </c>
+      <c r="L13" s="4">
+        <v>86.21644295302013</v>
+      </c>
+      <c r="M13" s="5">
+        <v>4</v>
+      </c>
+      <c r="N13" s="5">
+        <v>39129.58979606628</v>
+      </c>
+      <c r="O13" s="4">
+        <v>73.27638538589191</v>
+      </c>
+      <c r="P13" s="5">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>25</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.3163460404310326</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.3526468991041569</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.3681930103037741</v>
+      </c>
+      <c r="K14" s="4">
+        <v>93.88605442176872</v>
+      </c>
+      <c r="L14" s="4">
+        <v>91.03467561521258</v>
+      </c>
+      <c r="M14" s="5">
+        <v>4</v>
+      </c>
+      <c r="N14" s="5">
+        <v>198000.0476837158</v>
+      </c>
+      <c r="O14" s="4">
+        <v>404.081729966767</v>
+      </c>
+      <c r="P14" s="5">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>50</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>50</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>50</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.7077917657164219</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.3797428280938249</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.5234452314046931</v>
+      </c>
+      <c r="K15" s="4">
+        <v>78.51190476190482</v>
+      </c>
+      <c r="L15" s="4">
+        <v>78.21868008948574</v>
+      </c>
+      <c r="M15" s="5">
+        <v>4</v>
+      </c>
+      <c r="N15" s="5">
+        <v>344581.2447071075</v>
+      </c>
+      <c r="O15" s="4">
+        <v>418.6892402273481</v>
+      </c>
+      <c r="P15" s="5">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>100</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.5064419046673447</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.5064419046673447</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.6737875737879517</v>
+      </c>
+      <c r="K16" s="4">
+        <v>92.39795918367346</v>
+      </c>
+      <c r="L16" s="4">
+        <v>88.90380313199107</v>
+      </c>
+      <c r="M16" s="5">
+        <v>4</v>
+      </c>
+      <c r="N16" s="5">
+        <v>54246.37079238892</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.80941856537143</v>
+      </c>
+      <c r="P16" s="5">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>75</v>
+      </c>
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>25</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>25</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.473137324240369</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.3021074266432631</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.3366754032041255</v>
+      </c>
+      <c r="K17" s="4">
+        <v>87.90816326530613</v>
+      </c>
+      <c r="L17" s="4">
+        <v>88.65771812080537</v>
+      </c>
+      <c r="M17" s="5">
+        <v>4</v>
+      </c>
+      <c r="N17" s="5">
+        <v>59254.35447692871</v>
+      </c>
+      <c r="O17" s="4">
+        <v>115.5055642825121</v>
+      </c>
+      <c r="P17" s="5">
+        <v>513</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4178,9 +6460,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>4</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>2</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>0</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>4</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>2</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>3</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>3</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>2</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>2</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>4</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>0</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>3</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>1</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4191,9 +7228,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4227,8 +7270,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4250,173 +7301,243 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.2819327074736622</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.4265354830473926</v>
+      </c>
+      <c r="E3" s="4">
+        <v>72.27891156462584</v>
+      </c>
+      <c r="F3" s="4">
+        <v>58.53467561521252</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2819327074736622</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1737327078873241</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1737327078873241</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.52992434301916</v>
+      </c>
+      <c r="E4" s="4">
+        <v>81.32653061224489</v>
+      </c>
+      <c r="F4" s="4">
+        <v>85.68232662192393</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1737327078873241</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1737327078873241</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.1264875980163291</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.2297850994324014</v>
+      </c>
+      <c r="E5" s="4">
+        <v>71.63265306122449</v>
+      </c>
+      <c r="F5" s="4">
+        <v>73.36689038031319</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1264875980163291</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.1228777283299172</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>0.5504220610987938</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E6" s="4">
         <v>52.58503401360544</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F6" s="4">
         <v>47.80760626398209</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.1264875980163291</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.2297850994324014</v>
-      </c>
-      <c r="E4" s="4">
-        <v>71.63265306122449</v>
-      </c>
-      <c r="F4" s="4">
-        <v>73.36689038031319</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2819327074736622</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.4265354830473926</v>
-      </c>
-      <c r="E5" s="4">
-        <v>72.27891156462584</v>
-      </c>
-      <c r="F5" s="4">
-        <v>58.53467561521252</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.1737327078873241</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.1737327078873241</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.52992434301916</v>
-      </c>
-      <c r="E6" s="4">
-        <v>81.32653061224489</v>
-      </c>
-      <c r="F6" s="4">
-        <v>85.68232662192393</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.1228777283299172</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4427,14 +7548,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4445,9 +7567,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4481,8 +7609,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4504,149 +7640,201 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.3160670954436329</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <v>0.3163756090849903</v>
+      </c>
+      <c r="E3" s="4">
+        <v>28.5374149659864</v>
+      </c>
+      <c r="F3" s="4">
+        <v>29.32885906040269</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3160670954436329</v>
+      </c>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>3.683956096559199</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4">
+        <v>4.10589976110998</v>
+      </c>
+      <c r="E4" s="4">
+        <v>28.97959183673469</v>
+      </c>
+      <c r="F4" s="4">
+        <v>15.15659955257271</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>3.683956096559199</v>
+      </c>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.150065317556791</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.3142043499206826</v>
+      </c>
+      <c r="E5" s="4">
+        <v>34.21768707482993</v>
+      </c>
+      <c r="F5" s="4">
+        <v>29.02684563758389</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.150065317556791</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>2.46280299486039</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>3.056755173815469</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E6" s="4">
         <v>33.43537414965986</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F6" s="4">
         <v>12.97539149888143</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.150065317556791</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.3142043499206826</v>
-      </c>
-      <c r="E4" s="4">
-        <v>34.21768707482993</v>
-      </c>
-      <c r="F4" s="4">
-        <v>29.02684563758389</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.3160670954436329</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.3163756090849903</v>
-      </c>
-      <c r="E5" s="4">
-        <v>28.5374149659864</v>
-      </c>
-      <c r="F5" s="4">
-        <v>29.32885906040269</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>3.683956096559199</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>4.10589976110998</v>
-      </c>
-      <c r="E6" s="4">
-        <v>28.97959183673469</v>
-      </c>
-      <c r="F6" s="4">
-        <v>15.15659955257271</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -4668,9 +7856,23 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>2.46280299486039</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4681,14 +7883,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4699,9 +7902,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4735,8 +7944,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4758,149 +7975,215 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.09966858144101831</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.09966858144101831</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.04488769586381647</v>
+      </c>
+      <c r="E3" s="4">
+        <v>83.36734693877551</v>
+      </c>
+      <c r="F3" s="4">
+        <v>85.30201342281879</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09966858144101831</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09966858144101831</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.0129655996853435</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.0129655996853435</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1135238210255229</v>
+      </c>
+      <c r="E4" s="4">
+        <v>81.93877551020408</v>
+      </c>
+      <c r="F4" s="4">
+        <v>76.3758389261745</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.0129655996853435</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0129655996853435</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.09673443455941227</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.09673443455941227</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.05196124334580449</v>
+      </c>
+      <c r="E5" s="4">
+        <v>84.28571428571429</v>
+      </c>
+      <c r="F5" s="4">
+        <v>86.94630872483222</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09673443455941227</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09673443455941227</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.2414255106318199</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C6" s="4">
         <v>0.2414255106318199</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D6" s="4">
         <v>0.1007279121744835</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E6" s="4">
         <v>79.59183673469387</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F6" s="4">
         <v>80.57046979865771</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.09673443455941227</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.09673443455941227</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.05196124334580449</v>
-      </c>
-      <c r="E4" s="4">
-        <v>84.28571428571429</v>
-      </c>
-      <c r="F4" s="4">
-        <v>86.94630872483222</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.09966858144101831</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.09966858144101831</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.04488769586381647</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.36734693877551</v>
-      </c>
-      <c r="F5" s="4">
-        <v>85.30201342281879</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.0129655996853435</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.0129655996853435</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.1135238210255229</v>
-      </c>
-      <c r="E6" s="4">
-        <v>81.93877551020408</v>
-      </c>
-      <c r="F6" s="4">
-        <v>76.3758389261745</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -4922,9 +8205,25 @@
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.2414255106318199</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.2414255106318199</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4935,14 +8234,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4953,9 +8253,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4989,8 +8295,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5012,173 +8326,247 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.00657427723703119</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.00657427723703119</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.1035188395232227</v>
+      </c>
+      <c r="E3" s="4">
+        <v>93.36734693877551</v>
+      </c>
+      <c r="F3" s="4">
+        <v>94.22818791946308</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.00657427723703119</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.00657427723703119</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.02797608575281263</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.02797608575281263</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.06016058722082018</v>
+      </c>
+      <c r="E4" s="4">
+        <v>91.42857142857143</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.5503355704698</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.02797608575281263</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.02797608575281263</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2933078857207969</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.05800162275082615</v>
+      </c>
+      <c r="E5" s="4">
+        <v>77.34693877551021</v>
+      </c>
+      <c r="F5" s="4">
+        <v>71.64429530201342</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2933078857207969</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.4865912312138283</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>0.1271537655461037</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E6" s="4">
         <v>78.40136054421768</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F6" s="4">
         <v>70.79418344519016</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2933078857207969</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.05800162275082615</v>
-      </c>
-      <c r="E4" s="4">
-        <v>77.34693877551021</v>
-      </c>
-      <c r="F4" s="4">
-        <v>71.64429530201342</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.00657427723703119</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.00657427723703119</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1035188395232227</v>
-      </c>
-      <c r="E5" s="4">
-        <v>93.36734693877551</v>
-      </c>
-      <c r="F5" s="4">
-        <v>94.22818791946308</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.02797608575281263</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.02797608575281263</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.06016058722082018</v>
-      </c>
-      <c r="E6" s="4">
-        <v>91.42857142857143</v>
-      </c>
-      <c r="F6" s="4">
-        <v>92.5503355704698</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.4865912312138283</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5189,14 +8577,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:S6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -5207,9 +8596,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -5243,8 +8638,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5266,173 +8669,247 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
+        <v>0.01656376902761725</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.01656376902761725</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.03665482585134772</v>
+      </c>
+      <c r="E3" s="4">
+        <v>91.0204081632653</v>
+      </c>
+      <c r="F3" s="4">
+        <v>93.35570469798658</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4"/>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.01656376902761725</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.01656376902761725</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.1136580010360158</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1136580010360158</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.02507500848230482</v>
+      </c>
+      <c r="E4" s="4">
+        <v>87.65306122448979</v>
+      </c>
+      <c r="F4" s="4">
+        <v>89.02684563758389</v>
+      </c>
+      <c r="G4" s="5">
+        <v>1</v>
+      </c>
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4"/>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1136580010360158</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1136580010360158</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.2865930648589805</v>
+      </c>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
+        <v>0.1223717780852988</v>
+      </c>
+      <c r="E5" s="4">
+        <v>71.22448979591837</v>
+      </c>
+      <c r="F5" s="4">
+        <v>63.25503355704698</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2865930648589805</v>
+      </c>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="4">
         <v>0.5402954929936135</v>
       </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
         <v>0.3020891064274513</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E6" s="4">
         <v>77.75510204081633</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F6" s="4">
         <v>71.38702460850112</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.2865930648589805</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1223717780852988</v>
-      </c>
-      <c r="E4" s="4">
-        <v>71.22448979591837</v>
-      </c>
-      <c r="F4" s="4">
-        <v>63.25503355704698</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.01656376902761725</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.01656376902761725</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.03665482585134772</v>
-      </c>
-      <c r="E5" s="4">
-        <v>91.0204081632653</v>
-      </c>
-      <c r="F5" s="4">
-        <v>93.35570469798658</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.1136580010360158</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.1136580010360158</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.02507500848230482</v>
-      </c>
-      <c r="E6" s="4">
-        <v>87.65306122448979</v>
-      </c>
-      <c r="F6" s="4">
-        <v>89.02684563758389</v>
-      </c>
       <c r="G6" s="5">
         <v>1</v>
       </c>
       <c r="H6" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
       </c>
       <c r="J6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5">
         <v>0</v>
       </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="4">
+        <v>0.5402954929936135</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -5443,514 +8920,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3718682294708247</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3718682294708247</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.5060175209255542</v>
-      </c>
-      <c r="E3" s="4">
-        <v>81.83673469387755</v>
-      </c>
-      <c r="F3" s="4">
-        <v>78.7248322147651</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.04632243497934257</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.04632243497934257</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.1551878704670509</v>
-      </c>
-      <c r="E4" s="4">
-        <v>86.32653061224489</v>
-      </c>
-      <c r="F4" s="4">
-        <v>83.28859060402685</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.08353683517404153</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.08353683517404153</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1391111547974644</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.57142857142857</v>
-      </c>
-      <c r="F5" s="4">
-        <v>80.97315436241611</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.1104880175546805</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0.1104880175546805</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.2111916839165202</v>
-      </c>
-      <c r="E6" s="4">
-        <v>86.83673469387755</v>
-      </c>
-      <c r="F6" s="4">
-        <v>80.23489932885906</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5541165954005516</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.7466348296534813</v>
-      </c>
-      <c r="E3" s="4">
-        <v>22.95918367346939</v>
-      </c>
-      <c r="F3" s="4">
-        <v>8.970917225950783</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>0</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5742188839172646</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.5427314190124795</v>
-      </c>
-      <c r="E4" s="4">
-        <v>39.65986394557824</v>
-      </c>
-      <c r="F4" s="4">
-        <v>28.7472035794184</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>1.006053801223662</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.961687918350127</v>
-      </c>
-      <c r="E5" s="4">
-        <v>31.59863945578232</v>
-      </c>
-      <c r="F5" s="4">
-        <v>26.73378076062641</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="25" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.8688926199966991</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0.8992099265152538</v>
-      </c>
-      <c r="E6" s="4">
-        <v>33.19727891156463</v>
-      </c>
-      <c r="F6" s="4">
-        <v>17.49440715883669</v>
-      </c>
-      <c r="G6" s="5">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5">
-        <v>1</v>
-      </c>
-      <c r="K6" s="5">
-        <v>0</v>
-      </c>
-      <c r="L6" s="5">
-        <v>1</v>
-      </c>
-      <c r="M6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
